--- a/artfynd/A 57655-2023 artfynd.xlsx
+++ b/artfynd/A 57655-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129115218</v>
       </c>
       <c r="B2" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129114968</v>
       </c>
       <c r="B3" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129115796</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129115233</v>
       </c>
       <c r="B5" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129115026</v>
       </c>
       <c r="B6" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129115824</v>
       </c>
       <c r="B7" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129115194</v>
       </c>
       <c r="B8" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129115213</v>
       </c>
       <c r="B9" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129115148</v>
       </c>
       <c r="B10" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129115102</v>
       </c>
       <c r="B11" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129115132</v>
       </c>
       <c r="B12" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57655-2023 artfynd.xlsx
+++ b/artfynd/A 57655-2023 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115824</v>
+        <v>129115194</v>
       </c>
       <c r="B7" t="n">
-        <v>80175</v>
+        <v>80140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585964</v>
+        <v>585933</v>
       </c>
       <c r="R7" t="n">
-        <v>7038902</v>
+        <v>7038850</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129115194</v>
+        <v>129115824</v>
       </c>
       <c r="B8" t="n">
-        <v>80140</v>
+        <v>80175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585933</v>
+        <v>585964</v>
       </c>
       <c r="R8" t="n">
-        <v>7038850</v>
+        <v>7038902</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115102</v>
+        <v>129115132</v>
       </c>
       <c r="B11" t="n">
-        <v>80176</v>
+        <v>80140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585951</v>
+        <v>585952</v>
       </c>
       <c r="R11" t="n">
-        <v>7038879</v>
+        <v>7038849</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115132</v>
+        <v>129115102</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>80176</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585952</v>
+        <v>585951</v>
       </c>
       <c r="R12" t="n">
-        <v>7038849</v>
+        <v>7038879</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 57655-2023 artfynd.xlsx
+++ b/artfynd/A 57655-2023 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115194</v>
+        <v>129115824</v>
       </c>
       <c r="B7" t="n">
-        <v>80140</v>
+        <v>80175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585933</v>
+        <v>585964</v>
       </c>
       <c r="R7" t="n">
-        <v>7038850</v>
+        <v>7038902</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129115824</v>
+        <v>129115194</v>
       </c>
       <c r="B8" t="n">
-        <v>80175</v>
+        <v>80140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585964</v>
+        <v>585933</v>
       </c>
       <c r="R8" t="n">
-        <v>7038902</v>
+        <v>7038850</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115132</v>
+        <v>129115102</v>
       </c>
       <c r="B11" t="n">
-        <v>80140</v>
+        <v>80176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585952</v>
+        <v>585951</v>
       </c>
       <c r="R11" t="n">
-        <v>7038849</v>
+        <v>7038879</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115102</v>
+        <v>129115132</v>
       </c>
       <c r="B12" t="n">
-        <v>80176</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585951</v>
+        <v>585952</v>
       </c>
       <c r="R12" t="n">
-        <v>7038879</v>
+        <v>7038849</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 57655-2023 artfynd.xlsx
+++ b/artfynd/A 57655-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129115218</v>
       </c>
       <c r="B2" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129114968</v>
       </c>
       <c r="B3" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129115796</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129115233</v>
       </c>
       <c r="B5" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129115026</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129115824</v>
       </c>
       <c r="B7" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129115194</v>
       </c>
       <c r="B8" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129115213</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129115148</v>
       </c>
       <c r="B10" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129115102</v>
       </c>
       <c r="B11" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129115132</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57655-2023 artfynd.xlsx
+++ b/artfynd/A 57655-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129115218</v>
       </c>
       <c r="B2" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129114968</v>
       </c>
       <c r="B3" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129115796</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129115233</v>
       </c>
       <c r="B5" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129115026</v>
       </c>
       <c r="B6" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129115824</v>
       </c>
       <c r="B7" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129115194</v>
       </c>
       <c r="B8" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129115213</v>
       </c>
       <c r="B9" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129115148</v>
       </c>
       <c r="B10" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129115102</v>
       </c>
       <c r="B11" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129115132</v>
       </c>
       <c r="B12" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57655-2023 artfynd.xlsx
+++ b/artfynd/A 57655-2023 artfynd.xlsx
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115102</v>
+        <v>129115132</v>
       </c>
       <c r="B11" t="n">
-        <v>80182</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585951</v>
+        <v>585952</v>
       </c>
       <c r="R11" t="n">
-        <v>7038879</v>
+        <v>7038849</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115132</v>
+        <v>129115102</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>80182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585952</v>
+        <v>585951</v>
       </c>
       <c r="R12" t="n">
-        <v>7038849</v>
+        <v>7038879</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 57655-2023 artfynd.xlsx
+++ b/artfynd/A 57655-2023 artfynd.xlsx
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115132</v>
+        <v>129115102</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>80182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585952</v>
+        <v>585951</v>
       </c>
       <c r="R11" t="n">
-        <v>7038849</v>
+        <v>7038879</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115102</v>
+        <v>129115132</v>
       </c>
       <c r="B12" t="n">
-        <v>80182</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585951</v>
+        <v>585952</v>
       </c>
       <c r="R12" t="n">
-        <v>7038879</v>
+        <v>7038849</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 57655-2023 artfynd.xlsx
+++ b/artfynd/A 57655-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129115218</v>
       </c>
       <c r="B2" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129114968</v>
       </c>
       <c r="B3" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129115796</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129115233</v>
       </c>
       <c r="B5" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129115026</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129115824</v>
       </c>
       <c r="B7" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129115194</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129115213</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129115148</v>
       </c>
       <c r="B10" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115102</v>
+        <v>129115132</v>
       </c>
       <c r="B11" t="n">
-        <v>80182</v>
+        <v>80148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585951</v>
+        <v>585952</v>
       </c>
       <c r="R11" t="n">
-        <v>7038879</v>
+        <v>7038849</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115132</v>
+        <v>129115102</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>80184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585952</v>
+        <v>585951</v>
       </c>
       <c r="R12" t="n">
-        <v>7038849</v>
+        <v>7038879</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 57655-2023 artfynd.xlsx
+++ b/artfynd/A 57655-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129115218</v>
       </c>
       <c r="B2" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129114968</v>
       </c>
       <c r="B3" t="n">
-        <v>80176</v>
+        <v>80177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129115796</v>
       </c>
       <c r="B4" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129115233</v>
       </c>
       <c r="B5" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129115026</v>
       </c>
       <c r="B6" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129115824</v>
       </c>
       <c r="B7" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129115194</v>
       </c>
       <c r="B8" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129115213</v>
       </c>
       <c r="B9" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129115148</v>
       </c>
       <c r="B10" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115132</v>
+        <v>129115102</v>
       </c>
       <c r="B11" t="n">
-        <v>80148</v>
+        <v>80185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585952</v>
+        <v>585951</v>
       </c>
       <c r="R11" t="n">
-        <v>7038849</v>
+        <v>7038879</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115102</v>
+        <v>129115132</v>
       </c>
       <c r="B12" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585951</v>
+        <v>585952</v>
       </c>
       <c r="R12" t="n">
-        <v>7038879</v>
+        <v>7038849</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 57655-2023 artfynd.xlsx
+++ b/artfynd/A 57655-2023 artfynd.xlsx
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129115213</v>
+        <v>129115148</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585931</v>
+        <v>585954</v>
       </c>
       <c r="R9" t="n">
-        <v>7038859</v>
+        <v>7038840</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129115148</v>
+        <v>129115213</v>
       </c>
       <c r="B10" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585954</v>
+        <v>585931</v>
       </c>
       <c r="R10" t="n">
-        <v>7038840</v>
+        <v>7038859</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 57655-2023 artfynd.xlsx
+++ b/artfynd/A 57655-2023 artfynd.xlsx
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129115148</v>
+        <v>129115213</v>
       </c>
       <c r="B9" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585954</v>
+        <v>585931</v>
       </c>
       <c r="R9" t="n">
-        <v>7038840</v>
+        <v>7038859</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129115213</v>
+        <v>129115148</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585931</v>
+        <v>585954</v>
       </c>
       <c r="R10" t="n">
-        <v>7038859</v>
+        <v>7038840</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 57655-2023 artfynd.xlsx
+++ b/artfynd/A 57655-2023 artfynd.xlsx
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115102</v>
+        <v>129115132</v>
       </c>
       <c r="B11" t="n">
-        <v>80185</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585951</v>
+        <v>585952</v>
       </c>
       <c r="R11" t="n">
-        <v>7038879</v>
+        <v>7038849</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115132</v>
+        <v>129115102</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585952</v>
+        <v>585951</v>
       </c>
       <c r="R12" t="n">
-        <v>7038849</v>
+        <v>7038879</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 57655-2023 artfynd.xlsx
+++ b/artfynd/A 57655-2023 artfynd.xlsx
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115132</v>
+        <v>129115102</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>80185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585952</v>
+        <v>585951</v>
       </c>
       <c r="R11" t="n">
-        <v>7038849</v>
+        <v>7038879</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115102</v>
+        <v>129115132</v>
       </c>
       <c r="B12" t="n">
-        <v>80185</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585951</v>
+        <v>585952</v>
       </c>
       <c r="R12" t="n">
-        <v>7038879</v>
+        <v>7038849</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
